--- a/hackton_exercicio/limpo/orcamentos_limpo.xlsx
+++ b/hackton_exercicio/limpo/orcamentos_limpo.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,37 +421,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>setor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>valor_previsto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>valor_realizado</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>trimestre</t>
         </is>
@@ -487,7 +475,7 @@
       <c r="E2" t="n">
         <v>15524.52</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G2" t="n">
@@ -512,7 +500,7 @@
       <c r="E3" t="n">
         <v>45075.42</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="G3" t="n">
@@ -537,7 +525,7 @@
       <c r="E4" t="n">
         <v>44155.59</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="G4" t="n">
@@ -562,7 +550,7 @@
       <c r="E5" t="n">
         <v>59965.36</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="G5" t="n">
@@ -587,7 +575,7 @@
       <c r="E6" t="n">
         <v>15988.45</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="G6" t="n">
@@ -612,7 +600,7 @@
       <c r="E7" t="n">
         <v>70007.25999999999</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="G7" t="n">
@@ -637,7 +625,7 @@
       <c r="E8" t="n">
         <v>24831.97</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="G8" t="n">
@@ -662,7 +650,7 @@
       <c r="E9" t="n">
         <v>190453.57</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="G9" t="n">
@@ -687,7 +675,7 @@
       <c r="E10" t="n">
         <v>74191.09</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="G10" t="n">
@@ -712,7 +700,7 @@
       <c r="E11" t="n">
         <v>52639.94</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="G11" t="n">
@@ -737,7 +725,7 @@
       <c r="E12" t="n">
         <v>36631.54</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="G12" t="n">
@@ -762,7 +750,7 @@
       <c r="E13" t="n">
         <v>57310.21</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="G13" t="n">
@@ -787,7 +775,7 @@
       <c r="E14" t="n">
         <v>38493.2</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="G14" t="n">
@@ -812,7 +800,7 @@
       <c r="E15" t="n">
         <v>54142.85</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="G15" t="n">
@@ -837,7 +825,7 @@
       <c r="E16" t="n">
         <v>7177.94</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="G16" t="n">
@@ -862,7 +850,7 @@
       <c r="E17" t="n">
         <v>14807.27</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="G17" t="n">
@@ -887,7 +875,7 @@
       <c r="E18" t="n">
         <v>22518.62</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="G18" t="n">
@@ -912,7 +900,7 @@
       <c r="E19" t="n">
         <v>80783.09</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="G19" t="n">
@@ -937,7 +925,7 @@
       <c r="E20" t="n">
         <v>57572.04</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="G20" t="n">
@@ -962,7 +950,7 @@
       <c r="E21" t="n">
         <v>107587.09</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G21" t="n">
@@ -987,7 +975,7 @@
       <c r="E22" t="n">
         <v>65930.75999999999</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="G22" t="n">
@@ -1012,7 +1000,7 @@
       <c r="E23" t="n">
         <v>250588.6</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="G23" t="n">
@@ -1037,7 +1025,7 @@
       <c r="E24" t="n">
         <v>60835.27</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="G24" t="n">
@@ -1062,7 +1050,7 @@
       <c r="E25" t="n">
         <v>80835.77</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="G25" t="n">
@@ -1087,7 +1075,7 @@
       <c r="E26" t="n">
         <v>29802.86</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G26" t="n">
@@ -1112,7 +1100,7 @@
       <c r="E27" t="n">
         <v>92338.31</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="G27" t="n">
@@ -1137,7 +1125,7 @@
       <c r="E28" t="n">
         <v>75672.14</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="G28" t="n">
@@ -1162,7 +1150,7 @@
       <c r="E29" t="n">
         <v>102243.48</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="G29" t="n">
@@ -1187,7 +1175,7 @@
       <c r="E30" t="n">
         <v>44511.87</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="G30" t="n">
@@ -1212,7 +1200,7 @@
       <c r="E31" t="n">
         <v>55064.89</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="G31" t="n">
@@ -1237,7 +1225,7 @@
       <c r="E32" t="n">
         <v>22454.74</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="G32" t="n">
@@ -1262,7 +1250,7 @@
       <c r="E33" t="n">
         <v>64802.25</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="G33" t="n">
@@ -1287,7 +1275,7 @@
       <c r="E34" t="n">
         <v>31160.23</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="G34" t="n">
@@ -1312,7 +1300,7 @@
       <c r="E35" t="n">
         <v>31235.57</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="G35" t="n">
@@ -1337,7 +1325,7 @@
       <c r="E36" t="n">
         <v>43995.08</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="G36" t="n">
@@ -1362,7 +1350,7 @@
       <c r="E37" t="n">
         <v>15641.72</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="G37" t="n">
@@ -1387,7 +1375,7 @@
       <c r="E38" t="n">
         <v>89722.89999999999</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="G38" t="n">
@@ -1412,7 +1400,7 @@
       <c r="E39" t="n">
         <v>62430.81</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="G39" t="n">
@@ -1437,7 +1425,7 @@
       <c r="E40" t="n">
         <v>58195.23</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="G40" t="n">
@@ -1462,7 +1450,7 @@
       <c r="E41" t="n">
         <v>12655.33</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="G41" t="n">
@@ -1487,7 +1475,7 @@
       <c r="E42" t="n">
         <v>60727.49</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="G42" t="n">
@@ -1512,7 +1500,7 @@
       <c r="E43" t="n">
         <v>39331.9</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="G43" t="n">
@@ -1537,7 +1525,7 @@
       <c r="E44" t="n">
         <v>69753.39999999999</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="G44" t="n">
@@ -1562,7 +1550,7 @@
       <c r="E45" t="n">
         <v>68464.25999999999</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G45" t="n">
@@ -1587,7 +1575,7 @@
       <c r="E46" t="n">
         <v>62033.4</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="G46" t="n">
@@ -1612,7 +1600,7 @@
       <c r="E47" t="n">
         <v>52162.52</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="G47" t="n">
@@ -1637,7 +1625,7 @@
       <c r="E48" t="n">
         <v>100659.44</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="G48" t="n">
@@ -1662,7 +1650,7 @@
       <c r="E49" t="n">
         <v>62490.7</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="G49" t="n">
@@ -1687,7 +1675,7 @@
       <c r="E50" t="n">
         <v>46004.8</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G50" t="n">
@@ -1712,7 +1700,7 @@
       <c r="E51" t="n">
         <v>15295.32</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="G51" t="n">
@@ -1737,7 +1725,7 @@
       <c r="E52" t="n">
         <v>78253.08</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="G52" t="n">
@@ -1762,7 +1750,7 @@
       <c r="E53" t="n">
         <v>33847.05</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="G53" t="n">
@@ -1787,7 +1775,7 @@
       <c r="E54" t="n">
         <v>6843.26</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="G54" t="n">
@@ -1812,7 +1800,7 @@
       <c r="E55" t="n">
         <v>91167.89999999999</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="G55" t="n">
@@ -1837,7 +1825,7 @@
       <c r="E56" t="n">
         <v>64487.32</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="G56" t="n">
@@ -1862,7 +1850,7 @@
       <c r="E57" t="n">
         <v>54640.08</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="G57" t="n">
@@ -1887,7 +1875,7 @@
       <c r="E58" t="n">
         <v>42794.46</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F58" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="G58" t="n">
@@ -1912,7 +1900,7 @@
       <c r="E59" t="n">
         <v>73833.77</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="G59" t="n">
@@ -1937,7 +1925,7 @@
       <c r="E60" t="n">
         <v>89446.35000000001</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F60" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="G60" t="n">
@@ -1962,7 +1950,7 @@
       <c r="E61" t="n">
         <v>91357.84</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="G61" t="n">
@@ -1987,7 +1975,7 @@
       <c r="E62" t="n">
         <v>43657.87</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="G62" t="n">
@@ -2012,7 +2000,7 @@
       <c r="E63" t="n">
         <v>82462.00999999999</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="G63" t="n">
@@ -2037,7 +2025,7 @@
       <c r="E64" t="n">
         <v>10644.3</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="G64" t="n">
@@ -2062,7 +2050,7 @@
       <c r="E65" t="n">
         <v>47489.38</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="G65" t="n">
@@ -2087,7 +2075,7 @@
       <c r="E66" t="n">
         <v>313922.31</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="G66" t="n">
@@ -2112,7 +2100,7 @@
       <c r="E67" t="n">
         <v>69560.64</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F67" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="G67" t="n">
@@ -2137,7 +2125,7 @@
       <c r="E68" t="n">
         <v>32859.86</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F68" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="G68" t="n">
@@ -2162,7 +2150,7 @@
       <c r="E69" t="n">
         <v>18968.65</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F69" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G69" t="n">
@@ -2187,7 +2175,7 @@
       <c r="E70" t="n">
         <v>15485.26</v>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="F70" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="G70" t="n">
@@ -2212,7 +2200,7 @@
       <c r="E71" t="n">
         <v>70122.27</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="F71" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="G71" t="n">
@@ -2237,7 +2225,7 @@
       <c r="E72" t="n">
         <v>52224.21</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="F72" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="G72" t="n">
@@ -2262,7 +2250,7 @@
       <c r="E73" t="n">
         <v>43392.03</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F73" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="G73" t="n">
@@ -2287,7 +2275,7 @@
       <c r="E74" t="n">
         <v>45667.02</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F74" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G74" t="n">
@@ -2312,7 +2300,7 @@
       <c r="E75" t="n">
         <v>67783.19</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="F75" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="G75" t="n">
@@ -2337,7 +2325,7 @@
       <c r="E76" t="n">
         <v>69693.97</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="G76" t="n">
@@ -2362,7 +2350,7 @@
       <c r="E77" t="n">
         <v>65781.61</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="G77" t="n">
@@ -2387,7 +2375,7 @@
       <c r="E78" t="n">
         <v>25863.61</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F78" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="G78" t="n">
@@ -2412,7 +2400,7 @@
       <c r="E79" t="n">
         <v>72580.08</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F79" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="G79" t="n">
@@ -2437,7 +2425,7 @@
       <c r="E80" t="n">
         <v>33213.97</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F80" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="G80" t="n">
@@ -2462,7 +2450,7 @@
       <c r="E81" t="n">
         <v>56940.13</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="G81" t="n">
@@ -2487,7 +2475,7 @@
       <c r="E82" t="n">
         <v>54243.74</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="G82" t="n">
@@ -2512,7 +2500,7 @@
       <c r="E83" t="n">
         <v>63091.22</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="F83" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="G83" t="n">
@@ -2537,7 +2525,7 @@
       <c r="E84" t="n">
         <v>31420.39</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="F84" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="G84" t="n">
@@ -2562,7 +2550,7 @@
       <c r="E85" t="n">
         <v>104130.21</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="F85" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="G85" t="n">
@@ -2587,7 +2575,7 @@
       <c r="E86" t="n">
         <v>68597.09</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F86" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="G86" t="n">
@@ -2612,7 +2600,7 @@
       <c r="E87" t="n">
         <v>14153.24</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="F87" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="G87" t="n">
@@ -2637,7 +2625,7 @@
       <c r="E88" t="n">
         <v>61765.54</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="F88" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="G88" t="n">
@@ -2662,7 +2650,7 @@
       <c r="E89" t="n">
         <v>75961.67</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="F89" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="G89" t="n">
@@ -2687,7 +2675,7 @@
       <c r="E90" t="n">
         <v>118223.25</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="F90" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="G90" t="n">
@@ -2712,7 +2700,7 @@
       <c r="E91" t="n">
         <v>79148.08</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="F91" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="G91" t="n">
@@ -2737,7 +2725,7 @@
       <c r="E92" t="n">
         <v>40868.38</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="F92" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="G92" t="n">
@@ -2762,7 +2750,7 @@
       <c r="E93" t="n">
         <v>86438.99000000001</v>
       </c>
-      <c r="F93" s="2" t="n">
+      <c r="F93" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G93" t="n">
@@ -2787,7 +2775,7 @@
       <c r="E94" t="n">
         <v>33054.41</v>
       </c>
-      <c r="F94" s="2" t="n">
+      <c r="F94" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="G94" t="n">
@@ -2812,7 +2800,7 @@
       <c r="E95" t="n">
         <v>79152.83</v>
       </c>
-      <c r="F95" s="2" t="n">
+      <c r="F95" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="G95" t="n">
@@ -2837,7 +2825,7 @@
       <c r="E96" t="n">
         <v>91744.05</v>
       </c>
-      <c r="F96" s="2" t="n">
+      <c r="F96" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="G96" t="n">
@@ -2862,7 +2850,7 @@
       <c r="E97" t="n">
         <v>81371.36</v>
       </c>
-      <c r="F97" s="2" t="n">
+      <c r="F97" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="G97" t="n">
@@ -2887,7 +2875,7 @@
       <c r="E98" t="n">
         <v>6243.23</v>
       </c>
-      <c r="F98" s="2" t="n">
+      <c r="F98" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="G98" t="n">
@@ -2912,7 +2900,7 @@
       <c r="E99" t="n">
         <v>35370.84</v>
       </c>
-      <c r="F99" s="2" t="n">
+      <c r="F99" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="G99" t="n">
@@ -2937,7 +2925,7 @@
       <c r="E100" t="n">
         <v>48919.89</v>
       </c>
-      <c r="F100" s="2" t="n">
+      <c r="F100" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="G100" t="n">
@@ -2962,7 +2950,7 @@
       <c r="E101" t="n">
         <v>38720.18</v>
       </c>
-      <c r="F101" s="2" t="n">
+      <c r="F101" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="G101" t="n">
@@ -2987,7 +2975,7 @@
       <c r="E102" t="n">
         <v>11982.39</v>
       </c>
-      <c r="F102" s="2" t="n">
+      <c r="F102" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="G102" t="n">
@@ -3012,7 +3000,7 @@
       <c r="E103" t="n">
         <v>92918.12</v>
       </c>
-      <c r="F103" s="2" t="n">
+      <c r="F103" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="G103" t="n">
@@ -3037,7 +3025,7 @@
       <c r="E104" t="n">
         <v>76111.14999999999</v>
       </c>
-      <c r="F104" s="2" t="n">
+      <c r="F104" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="G104" t="n">
@@ -3062,7 +3050,7 @@
       <c r="E105" t="n">
         <v>88679.42999999999</v>
       </c>
-      <c r="F105" s="2" t="n">
+      <c r="F105" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="G105" t="n">
@@ -3087,7 +3075,7 @@
       <c r="E106" t="n">
         <v>33435.05</v>
       </c>
-      <c r="F106" s="2" t="n">
+      <c r="F106" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="G106" t="n">
@@ -3112,7 +3100,7 @@
       <c r="E107" t="n">
         <v>70867.72</v>
       </c>
-      <c r="F107" s="2" t="n">
+      <c r="F107" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="G107" t="n">
@@ -3137,7 +3125,7 @@
       <c r="E108" t="n">
         <v>51053.38</v>
       </c>
-      <c r="F108" s="2" t="n">
+      <c r="F108" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="G108" t="n">
@@ -3162,7 +3150,7 @@
       <c r="E109" t="n">
         <v>22170.43</v>
       </c>
-      <c r="F109" s="2" t="n">
+      <c r="F109" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="G109" t="n">
@@ -3187,7 +3175,7 @@
       <c r="E110" t="n">
         <v>76641.07000000001</v>
       </c>
-      <c r="F110" s="2" t="n">
+      <c r="F110" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="G110" t="n">
@@ -3212,7 +3200,7 @@
       <c r="E111" t="n">
         <v>76971.06</v>
       </c>
-      <c r="F111" s="2" t="n">
+      <c r="F111" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="G111" t="n">
@@ -3237,7 +3225,7 @@
       <c r="E112" t="n">
         <v>31529.24</v>
       </c>
-      <c r="F112" s="2" t="n">
+      <c r="F112" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="G112" t="n">
@@ -3262,7 +3250,7 @@
       <c r="E113" t="n">
         <v>41566.93</v>
       </c>
-      <c r="F113" s="2" t="n">
+      <c r="F113" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="G113" t="n">
@@ -3287,7 +3275,7 @@
       <c r="E114" t="n">
         <v>81075.45</v>
       </c>
-      <c r="F114" s="2" t="n">
+      <c r="F114" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="G114" t="n">
@@ -3312,7 +3300,7 @@
       <c r="E115" t="n">
         <v>17731.1</v>
       </c>
-      <c r="F115" s="2" t="n">
+      <c r="F115" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="G115" t="n">
@@ -3337,7 +3325,7 @@
       <c r="E116" t="n">
         <v>57251.65</v>
       </c>
-      <c r="F116" s="2" t="n">
+      <c r="F116" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="G116" t="n">
@@ -3362,7 +3350,7 @@
       <c r="E117" t="n">
         <v>63496.66</v>
       </c>
-      <c r="F117" s="2" t="n">
+      <c r="F117" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="G117" t="n">
@@ -3387,7 +3375,7 @@
       <c r="E118" t="n">
         <v>270703.31</v>
       </c>
-      <c r="F118" s="2" t="n">
+      <c r="F118" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="G118" t="n">
@@ -3412,7 +3400,7 @@
       <c r="E119" t="n">
         <v>43491.56</v>
       </c>
-      <c r="F119" s="2" t="n">
+      <c r="F119" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="G119" t="n">
@@ -3437,7 +3425,7 @@
       <c r="E120" t="n">
         <v>92876.92999999999</v>
       </c>
-      <c r="F120" s="2" t="n">
+      <c r="F120" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="G120" t="n">
@@ -3462,7 +3450,7 @@
       <c r="E121" t="n">
         <v>5623.75</v>
       </c>
-      <c r="F121" s="2" t="n">
+      <c r="F121" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="G121" t="n">
